--- a/재무비율_결과.xlsx
+++ b/재무비율_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,26 @@
           <t>재고회전율(회)</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>영업이익률(%)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>순이익률(%)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ROA(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ROE(%)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -445,13 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.36</v>
+        <v>29.94</v>
       </c>
       <c r="C2" t="n">
-        <v>258.77</v>
+        <v>232.76</v>
       </c>
       <c r="D2" t="n">
-        <v>5.02</v>
+        <v>6.34</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10.36</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +493,53 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87.52</v>
+        <v>45.95</v>
       </c>
       <c r="C3" t="n">
-        <v>145.03</v>
+        <v>185.82</v>
       </c>
       <c r="D3" t="n">
-        <v>2.43</v>
+        <v>6.8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="F3" t="n">
+        <v>44.21</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="H3" t="n">
+        <v>35.59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>야놀자</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>128.34</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="D4" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-2.54</v>
       </c>
     </row>
   </sheetData>
